--- a/tests/fixtures/qualification_workbook_unrecalculated.xlsx
+++ b/tests/fixtures/qualification_workbook_unrecalculated.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1422,6 +1422,194 @@
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Function outside the catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>and_all_true</t>
+        </is>
+      </c>
+      <c r="B36" s="5">
+        <f>IF(AND(TRUE,TRUE,TRUE),1,0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>and_one_false</t>
+        </is>
+      </c>
+      <c r="B37" s="5">
+        <f>IF(AND(TRUE,FALSE,TRUE),1,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>or_one_true</t>
+        </is>
+      </c>
+      <c r="B38" s="5">
+        <f>IF(OR(FALSE,TRUE,FALSE),1,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>or_all_false</t>
+        </is>
+      </c>
+      <c r="B39" s="5">
+        <f>IF(OR(FALSE,FALSE,FALSE),1,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>sumproduct_2d</t>
+        </is>
+      </c>
+      <c r="B40" s="5">
+        <f>SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
+        <v/>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>npv_cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" s="5">
+        <f>NPV(0.1,-1000,300,300,300)</f>
+        <v/>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>-230.8585</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Excel convention: first flow at period 1, not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>choose_index_1</t>
+        </is>
+      </c>
+      <c r="B42" s="5">
+        <f>CHOOSE(1,10,20,30)</f>
+        <v/>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>choose_index_2</t>
+        </is>
+      </c>
+      <c r="B43" s="5">
+        <f>CHOOSE(2,10,20,30)</f>
+        <v/>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>xlookup_exact</t>
+        </is>
+      </c>
+      <c r="B44" s="5">
+        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>XLOOKUP not in Excel/LibreOffice; VLOOKUP-equivalent formula used for fixture</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/qualification_workbook_unrecalculated.xlsx
+++ b/tests/fixtures/qualification_workbook_unrecalculated.xlsx
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B44" s="5">
-        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE)</f>
+        <f>_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
         <v/>
       </c>
       <c r="C44" s="5" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP not in Excel/LibreOffice; VLOOKUP-equivalent formula used for fixture</t>
+          <t>Exact numeric XLOOKUP, recalculated through LibreOffice</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/qualification_workbook_unrecalculated.xlsx
+++ b/tests/fixtures/qualification_workbook_unrecalculated.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualification" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross Tab" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Qualification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cross Tab" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Errors" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Guide" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1610,6 +1610,102 @@
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Exact numeric XLOOKUP, recalculated through LibreOffice</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>date_leap_day</t>
+        </is>
+      </c>
+      <c r="B45" s="5">
+        <f>DATE(2024,2,29)</f>
+        <v/>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Leap-day construction as an Excel serial date</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>edate_month_end_clamp</t>
+        </is>
+      </c>
+      <c r="B46" s="5">
+        <f>EDATE(DATE(2024,1,31),1)</f>
+        <v/>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>January month-end clamps to the 2024 leap day</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>networkdays_inclusive_week</t>
+        </is>
+      </c>
+      <c r="B47" s="5">
+        <f>NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,7))</f>
+        <v/>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Inclusive Monday-to-Sunday working-day count</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>yearfrac_actual_365_leap_year</t>
+        </is>
+      </c>
+      <c r="B48" s="5">
+        <f>YEARFRAC(DATE(2024,1,1),DATE(2025,1,1),3)</f>
+        <v/>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>1.002739726027397</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Actual/365 basis across the 2024 leap year</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/qualification_workbook_unrecalculated.xlsx
+++ b/tests/fixtures/qualification_workbook_unrecalculated.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -784,143 +784,151 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>abs_negative</t>
+          <t>max_mixed_range</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>ABS(Inputs!$B$6)</f>
+        <f>MAX(Inputs!$B$4:$B$8)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Blank cell excluded from consideration, not treated as 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>int_negative</t>
+          <t>min_mixed_range</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>INT(-1.2)</f>
+        <f>MIN(Inputs!$B$4:$B$8)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Blank cell excluded from consideration, not treated as 0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>round_positive_half</t>
+          <t>abs_negative</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>ROUND(2.5,0)</f>
+        <f>ABS(Inputs!$B$6)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Excel half away from zero</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>round_negative_half</t>
+          <t>int_negative</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <f>ROUND(-2.5,0)</f>
+        <f>INT(-1.2)</f>
         <v/>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Excel half away from zero</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>roundup_negative</t>
+          <t>round_positive_half</t>
         </is>
       </c>
       <c r="B9" s="5">
-        <f>ROUNDUP(-1.21,1)</f>
+        <f>ROUND(2.5,0)</f>
         <v/>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-1.3</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Excel half away from zero</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>rounddown_negative</t>
+          <t>round_negative_half</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <f>ROUNDDOWN(-1.29,1)</f>
+        <f>ROUND(-2.5,0)</f>
         <v/>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Excel half away from zero</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ceiling_positive</t>
+          <t>roundup_negative</t>
         </is>
       </c>
       <c r="B11" s="5">
-        <f>CEILING(2.1,0.5)</f>
+        <f>ROUNDUP(-1.21,1)</f>
         <v/>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2.5</v>
+        <v>-1.3</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
@@ -932,15 +940,15 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>floor_positive</t>
+          <t>rounddown_negative</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <f>FLOOR(2.9,0.5)</f>
+        <f>ROUNDDOWN(-1.29,1)</f>
         <v/>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2.5</v>
+        <v>-1.2</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -952,15 +960,15 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>sumif_text</t>
+          <t>ceiling_positive</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <f>SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
+        <f>CEILING(2.1,0.5)</f>
         <v/>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
@@ -972,15 +980,15 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>sumifs_text_region</t>
+          <t>floor_positive</t>
         </is>
       </c>
       <c r="B14" s="5">
-        <f>SUMIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
+        <f>FLOOR(2.9,0.5)</f>
         <v/>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
@@ -992,15 +1000,15 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>countif_text</t>
+          <t>sumif_text</t>
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Inputs!$A$4:$A$8,"Motor")</f>
+        <f>SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
         <v/>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -1012,103 +1020,103 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>countifs_boolean</t>
+          <t>sumifs_text_region</t>
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS(Inputs!$A$4:$A$8,"Motor",Inputs!$D$4:$D$8,TRUE())</f>
+        <f>SUMIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
         <v/>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>TRUE() boolean call in a criteria function</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>averageif_blank_zero</t>
+          <t>countif_text</t>
         </is>
       </c>
       <c r="B17" s="5">
-        <f>AVERAGEIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
+        <f>COUNTIF(Inputs!$A$4:$A$8,"Motor")</f>
         <v/>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>A literal zero contributes to the denominator</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>averageifs_text_region</t>
+          <t>countifs_boolean</t>
         </is>
       </c>
       <c r="B18" s="5">
-        <f>AVERAGEIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
+        <f>COUNTIFS(Inputs!$A$4:$A$8,"Motor",Inputs!$D$4:$D$8,TRUE())</f>
         <v/>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>TRUE() boolean call in a criteria function</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>minifs_text</t>
+          <t>averageif_blank_zero</t>
         </is>
       </c>
       <c r="B19" s="5">
-        <f>_xlfn.MINIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
+        <f>AVERAGEIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
         <v/>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>A literal zero contributes to the denominator</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>maxifs_text</t>
+          <t>averageifs_text_region</t>
         </is>
       </c>
       <c r="B20" s="5">
-        <f>_xlfn.MAXIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
+        <f>AVERAGEIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
         <v/>
       </c>
       <c r="C20" s="5" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
@@ -1120,15 +1128,15 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>if_true_literal</t>
+          <t>minifs_text</t>
         </is>
       </c>
       <c r="B21" s="5">
-        <f>IF(TRUE,11,22)</f>
+        <f>_xlfn.MINIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
         <v/>
       </c>
       <c r="C21" s="5" t="n">
-        <v>11</v>
+        <v>-5</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1140,15 +1148,15 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>if_false_literal</t>
+          <t>maxifs_text</t>
         </is>
       </c>
       <c r="B22" s="5">
-        <f>IF(FALSE,11,22)</f>
+        <f>_xlfn.MAXIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
         <v/>
       </c>
       <c r="C22" s="5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
@@ -1160,11 +1168,11 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>if_true_call</t>
+          <t>if_true_literal</t>
         </is>
       </c>
       <c r="B23" s="5">
-        <f>IF(TRUE(),11,22)</f>
+        <f>IF(TRUE,11,22)</f>
         <v/>
       </c>
       <c r="C23" s="5" t="n">
@@ -1180,11 +1188,11 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>if_false_call</t>
+          <t>if_false_literal</t>
         </is>
       </c>
       <c r="B24" s="5">
-        <f>IF(FALSE(),11,22)</f>
+        <f>IF(FALSE,11,22)</f>
         <v/>
       </c>
       <c r="C24" s="5" t="n">
@@ -1200,15 +1208,15 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>vlookup_exact</t>
+          <t>if_true_call</t>
         </is>
       </c>
       <c r="B25" s="5">
-        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE())</f>
+        <f>IF(TRUE(),11,22)</f>
         <v/>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
@@ -1220,15 +1228,15 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>match_exact</t>
+          <t>if_false_call</t>
         </is>
       </c>
       <c r="B26" s="5">
-        <f>MATCH("Liability",Inputs!$E$4:$E$6,0)</f>
+        <f>IF(FALSE(),11,22)</f>
         <v/>
       </c>
       <c r="C26" s="5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -1240,11 +1248,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>index_scalar</t>
+          <t>vlookup_exact</t>
         </is>
       </c>
       <c r="B27" s="5">
-        <f>INDEX(Inputs!$F$4:$F$6,2)</f>
+        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE())</f>
         <v/>
       </c>
       <c r="C27" s="5" t="n">
@@ -1260,15 +1268,15 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>index_match_nested</t>
+          <t>match_exact</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <f>INDEX(Inputs!$F$4:$F$6,MATCH("Liability",Inputs!$E$4:$E$6,0))</f>
+        <f>MATCH("Liability",Inputs!$E$4:$E$6,0)</f>
         <v/>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -1280,15 +1288,15 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>nested_round_sumif</t>
+          <t>index_scalar</t>
         </is>
       </c>
       <c r="B29" s="5">
-        <f>ROUND(SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8),2)</f>
+        <f>INDEX(Inputs!$F$4:$F$6,2)</f>
         <v/>
       </c>
       <c r="C29" s="5" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
@@ -1300,15 +1308,15 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>cross_tab_range</t>
+          <t>index_match_nested</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <f>SUM('Cross Tab'!$B$3:$B$5)</f>
+        <f>INDEX(Inputs!$F$4:$F$6,MATCH("Liability",Inputs!$E$4:$E$6,0))</f>
         <v/>
       </c>
       <c r="C30" s="5" t="n">
-        <v>20</v>
+        <v>1.3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -1320,15 +1328,15 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ordinary_arithmetic</t>
+          <t>nested_round_sumif</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <f>(Inputs!$B$4+Inputs!$B$5)*2/3</f>
+        <f>ROUND(SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8),2)</f>
         <v/>
       </c>
       <c r="C31" s="5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
@@ -1340,55 +1348,51 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>vlookup_approximate_unsupported</t>
+          <t>cross_tab_range</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,TRUE())</f>
-        <v/>
-      </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Approximate lookup must fail closed</t>
-        </is>
-      </c>
+        <f>SUM('Cross Tab'!$B$3:$B$5)</f>
+        <v/>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>match_approximate_unsupported</t>
+          <t>ordinary_arithmetic</t>
         </is>
       </c>
       <c r="B33" s="5">
-        <f>MATCH("Property",Inputs!$E$4:$E$6,1)</f>
-        <v/>
-      </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Approximate MATCH must fail closed</t>
-        </is>
-      </c>
+        <f>(Inputs!$B$4+Inputs!$B$5)*2/3</f>
+        <v/>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>index_array_unsupported</t>
+          <t>vlookup_approximate_unsupported</t>
         </is>
       </c>
       <c r="B34" s="5">
-        <f>INDEX(Inputs!$B$4:$B$8,0)</f>
+        <f>VLOOKUP("Property",Inputs!$E$4:$F$6,2,TRUE())</f>
         <v/>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -1399,18 +1403,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Array result must not be silently reduced to a scalar</t>
+          <t>Approximate lookup must fail closed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>offset_unsupported</t>
+          <t>match_approximate_unsupported</t>
         </is>
       </c>
       <c r="B35" s="5">
-        <f>OFFSET(Inputs!$B$4,1,0)</f>
+        <f>MATCH("Property",Inputs!$E$4:$E$6,1)</f>
         <v/>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -1421,58 +1425,62 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Function outside the catalogue</t>
+          <t>Approximate MATCH must fail closed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>and_all_true</t>
+          <t>index_array_unsupported</t>
         </is>
       </c>
       <c r="B36" s="5">
-        <f>IF(AND(TRUE,TRUE,TRUE),1,0)</f>
-        <v/>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+        <f>INDEX(Inputs!$B$4:$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Array result must not be silently reduced to a scalar</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>and_one_false</t>
+          <t>offset_unsupported</t>
         </is>
       </c>
       <c r="B37" s="5">
-        <f>IF(AND(TRUE,FALSE,TRUE),1,0)</f>
-        <v/>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+        <f>OFFSET(Inputs!$B$4,1,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Function outside the catalogue</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>or_one_true</t>
+          <t>and_all_true</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <f>IF(OR(FALSE,TRUE,FALSE),1,0)</f>
+        <f>IF(AND(TRUE,TRUE,TRUE),1,0)</f>
         <v/>
       </c>
       <c r="C38" s="5" t="n">
@@ -1488,11 +1496,11 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>or_all_false</t>
+          <t>and_one_false</t>
         </is>
       </c>
       <c r="B39" s="5">
-        <f>IF(OR(FALSE,FALSE,FALSE),1,0)</f>
+        <f>IF(AND(TRUE,FALSE,TRUE),1,0)</f>
         <v/>
       </c>
       <c r="C39" s="5" t="n">
@@ -1508,15 +1516,15 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>sumproduct_2d</t>
+          <t>or_one_true</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <f>SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
+        <f>IF(OR(FALSE,TRUE,FALSE),1,0)</f>
         <v/>
       </c>
       <c r="C40" s="5" t="n">
-        <v>28.5</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
@@ -1528,39 +1536,35 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>npv_cash_flow</t>
+          <t>or_all_false</t>
         </is>
       </c>
       <c r="B41" s="5">
-        <f>NPV(0.1,-1000,300,300,300)</f>
+        <f>IF(OR(FALSE,FALSE,FALSE),1,0)</f>
         <v/>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-230.8585</v>
+        <v>0</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Excel convention: first flow at period 1, not 0</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>choose_index_1</t>
+          <t>sumproduct_2d</t>
         </is>
       </c>
       <c r="B42" s="5">
-        <f>CHOOSE(1,10,20,30)</f>
+        <f>SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
         <v/>
       </c>
       <c r="C42" s="5" t="n">
-        <v>10</v>
+        <v>28.5</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
@@ -1572,83 +1576,79 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>choose_index_2</t>
+          <t>npv_cash_flow</t>
         </is>
       </c>
       <c r="B43" s="5">
-        <f>CHOOSE(2,10,20,30)</f>
+        <f>NPV(0.1,-1000,300,300,300)</f>
         <v/>
       </c>
       <c r="C43" s="5" t="n">
-        <v>20</v>
+        <v>-230.8585</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Excel convention: first flow at period 1, not 0</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>xlookup_exact</t>
+          <t>choose_index_1</t>
         </is>
       </c>
       <c r="B44" s="5">
-        <f>_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
+        <f>CHOOSE(1,10,20,30)</f>
         <v/>
       </c>
       <c r="C44" s="5" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Exact numeric XLOOKUP, recalculated through LibreOffice</t>
-        </is>
-      </c>
+      <c r="E44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>date_leap_day</t>
+          <t>choose_index_2</t>
         </is>
       </c>
       <c r="B45" s="5">
-        <f>DATE(2024,2,29)</f>
+        <f>CHOOSE(2,10,20,30)</f>
         <v/>
       </c>
       <c r="C45" s="5" t="n">
-        <v>45351</v>
+        <v>20</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Leap-day construction as an Excel serial date</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>edate_month_end_clamp</t>
+          <t>xlookup_exact</t>
         </is>
       </c>
       <c r="B46" s="5">
-        <f>EDATE(DATE(2024,1,31),1)</f>
+        <f>_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
         <v/>
       </c>
       <c r="C46" s="5" t="n">
-        <v>45351</v>
+        <v>1.2</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>January month-end clamps to the 2024 leap day</t>
+          <t>Exact numeric XLOOKUP, recalculated through LibreOffice</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>networkdays_inclusive_week</t>
+          <t>date_leap_day</t>
         </is>
       </c>
       <c r="B47" s="5">
-        <f>NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,7))</f>
+        <f>DATE(2024,2,29)</f>
         <v/>
       </c>
       <c r="C47" s="5" t="n">
-        <v>5</v>
+        <v>45351</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
@@ -1681,29 +1681,77 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Inclusive Monday-to-Sunday working-day count</t>
+          <t>Leap-day construction as an Excel serial date</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>edate_month_end_clamp</t>
+        </is>
+      </c>
+      <c r="B48" s="5">
+        <f>EDATE(DATE(2024,1,31),1)</f>
+        <v/>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>January month-end clamps to the 2024 leap day</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>networkdays_inclusive_week</t>
+        </is>
+      </c>
+      <c r="B49" s="5">
+        <f>NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,7))</f>
+        <v/>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Inclusive Monday-to-Sunday working-day count</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>yearfrac_actual_365_leap_year</t>
         </is>
       </c>
-      <c r="B48" s="5">
+      <c r="B50" s="5">
         <f>YEARFRAC(DATE(2024,1,1),DATE(2025,1,1),3)</f>
         <v/>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C50" s="5" t="n">
         <v>1.002739726027397</v>
       </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Actual/365 basis across the 2024 leap year</t>
         </is>
